--- a/E/TH1MKT.xlsx
+++ b/E/TH1MKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="50">
   <si>
     <t/>
   </si>
   <si>
-    <t>20002988</t>
-  </si>
-  <si>
-    <t>KUSUKA KRP AYM LD 60</t>
+    <t>20139550</t>
+  </si>
+  <si>
+    <t>REGEN LMN LIME 300ML</t>
   </si>
   <si>
     <t>TH1MKT</t>
@@ -28,127 +28,103 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20002989</t>
-  </si>
-  <si>
-    <t>KUSUKA KRP KJ.BKR 60</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20141124</t>
+  </si>
+  <si>
+    <t>REGEN ORANGE 300ML</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20091225</t>
-  </si>
-  <si>
-    <t>OVLTNE CHO BISC 104G</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>10016646</t>
-  </si>
-  <si>
-    <t>INDO/F KECAP MN.R725</t>
-  </si>
-  <si>
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>20136277</t>
-  </si>
-  <si>
-    <t>SNPRD FRT MG.PINE220</t>
-  </si>
-  <si>
-    <t>20120928</t>
-  </si>
-  <si>
-    <t>IM-BOOST VIT C&amp;D3 4S</t>
+    <t>20128233</t>
+  </si>
+  <si>
+    <t>NU CHO TEA HZLTEA330</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>20137510</t>
-  </si>
-  <si>
-    <t>C/LANG KY PTH ROL 15</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20062306</t>
-  </si>
-  <si>
-    <t>RXONA MEN DEO ICE 45</t>
+    <t>20138202</t>
+  </si>
+  <si>
+    <t>NU MATCHA LATTEA 330</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20040383</t>
+  </si>
+  <si>
+    <t>NU MILK TEA 330ML</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20069527</t>
+  </si>
+  <si>
+    <t>NU TEH TARIK 330ML</t>
+  </si>
+  <si>
+    <t>20087713</t>
+  </si>
+  <si>
+    <t>IDM NDL AYM PDS 90G</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20129840</t>
+  </si>
+  <si>
+    <t>IDM MIE GRG INDO 88G</t>
+  </si>
+  <si>
+    <t>20129841</t>
+  </si>
+  <si>
+    <t>IDM MIE GRG PDS 92G</t>
+  </si>
+  <si>
+    <t>20091175</t>
+  </si>
+  <si>
+    <t>PEPSODNT KIDS STR 45</t>
   </si>
   <si>
     <t>PT,(E-3B)</t>
   </si>
   <si>
-    <t>20062307</t>
-  </si>
-  <si>
-    <t>RXONA MEN DEO INV 50</t>
-  </si>
-  <si>
-    <t>20062308</t>
-  </si>
-  <si>
-    <t>RXONA MEN DEO SPR 45</t>
-  </si>
-  <si>
-    <t>20062309</t>
-  </si>
-  <si>
-    <t>RXNA MEN DEO ULTR 45</t>
-  </si>
-  <si>
-    <t>20139354</t>
-  </si>
-  <si>
-    <t>RXONA MEN FR.STRK 40</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20139522</t>
-  </si>
-  <si>
-    <t>RXONA MEN DRY DEF 40</t>
-  </si>
-  <si>
-    <t>10040202</t>
-  </si>
-  <si>
-    <t>SOFFELL A.NYMK K/J60</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>RT,(E-3.5B)</t>
-  </si>
-  <si>
-    <t>20078241</t>
-  </si>
-  <si>
-    <t>SOFFELL LOT.APEL 60G</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20128713</t>
-  </si>
-  <si>
-    <t>SOFEL LOT.KRN/SMR 60</t>
+    <t>10037208</t>
+  </si>
+  <si>
+    <t>CLOSE UP MT.FRSH 110</t>
+  </si>
+  <si>
+    <t>20027167</t>
+  </si>
+  <si>
+    <t>IDM FAC.TISSUE NP400</t>
+  </si>
+  <si>
+    <t>20104950</t>
+  </si>
+  <si>
+    <t>RINSO MLTO JP/PCH510</t>
+  </si>
+  <si>
+    <t>PT</t>
   </si>
   <si>
     <t>20054750</t>
@@ -157,21 +133,12 @@
     <t>RNSO+ML LIQ PRFM 510</t>
   </si>
   <si>
-    <t>PT</t>
-  </si>
-  <si>
     <t>20093188</t>
   </si>
   <si>
     <t>RINSO MLTO GLD LQ510</t>
   </si>
   <si>
-    <t>20104950</t>
-  </si>
-  <si>
-    <t>RINSO MLTO JP/PCH510</t>
-  </si>
-  <si>
     <t>20122879</t>
   </si>
   <si>
@@ -188,6 +155,12 @@
   </si>
   <si>
     <t>RINSO PURE LIQ 510G</t>
+  </si>
+  <si>
+    <t>20112492</t>
+  </si>
+  <si>
+    <t>SUNLIGHT JRK NPS400G</t>
   </si>
 </sst>
 </file>
@@ -580,14 +553,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -647,127 +620,127 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F7" s="1" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -781,13 +754,13 @@
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -801,53 +774,53 @@
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -861,193 +834,133 @@
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/E/TH1MKT.xlsx
+++ b/E/TH1MKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="78">
   <si>
     <t/>
   </si>
   <si>
-    <t>20139550</t>
-  </si>
-  <si>
-    <t>REGEN LMN LIME 300ML</t>
+    <t>20138893</t>
+  </si>
+  <si>
+    <t>AMO DRMY STRAW 180ML</t>
   </si>
   <si>
     <t>TH1MKT</t>
@@ -31,136 +31,220 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20141124</t>
-  </si>
-  <si>
-    <t>REGEN ORANGE 300ML</t>
+    <t>20138894</t>
+  </si>
+  <si>
+    <t>AMO FIZZY EASY 180ML</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
+    <t>20003567</t>
+  </si>
+  <si>
+    <t>SASA T.BUMBU ORG 210</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>20128233</t>
-  </si>
-  <si>
-    <t>NU CHO TEA HZLTEA330</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20138202</t>
-  </si>
-  <si>
-    <t>NU MATCHA LATTEA 330</t>
+    <t>20003568</t>
+  </si>
+  <si>
+    <t>SASA T.BUMBU SPIC210</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>20040383</t>
-  </si>
-  <si>
-    <t>NU MILK TEA 330ML</t>
+    <t>20014694</t>
+  </si>
+  <si>
+    <t>SASA TPNG G.PISNG210</t>
+  </si>
+  <si>
+    <t>20041881</t>
+  </si>
+  <si>
+    <t>SASA T.BMB KENTKY200</t>
+  </si>
+  <si>
+    <t>20065236</t>
+  </si>
+  <si>
+    <t>SASA TPNG BKWAN 225G</t>
+  </si>
+  <si>
+    <t>10000726</t>
+  </si>
+  <si>
+    <t>ASTOR CHOCOLATE 150G</t>
+  </si>
+  <si>
+    <t>20137700</t>
+  </si>
+  <si>
+    <t>MAYASI CSHW KTCY 35G</t>
+  </si>
+  <si>
+    <t>10037405</t>
+  </si>
+  <si>
+    <t>C/LANG KAYU PUTIH 30</t>
+  </si>
+  <si>
+    <t>RT,(E-6B)</t>
+  </si>
+  <si>
+    <t>20139593</t>
+  </si>
+  <si>
+    <t>FCARE VPOBALM MATCHA</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20037203</t>
+  </si>
+  <si>
+    <t>FRESH/C MYK ANG LV10</t>
+  </si>
+  <si>
+    <t>20040719</t>
+  </si>
+  <si>
+    <t>FRESH/C MYK/A STRG10</t>
+  </si>
+  <si>
+    <t>20139612</t>
+  </si>
+  <si>
+    <t>FCARE SMASH FRUITY</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>20069527</t>
-  </si>
-  <si>
-    <t>NU TEH TARIK 330ML</t>
-  </si>
-  <si>
-    <t>20087713</t>
-  </si>
-  <si>
-    <t>IDM NDL AYM PDS 90G</t>
+    <t>20034536</t>
+  </si>
+  <si>
+    <t>FRESH/C MNYK ANGIN10</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20131218</t>
+  </si>
+  <si>
+    <t>FRS.CR SMASH IN+R/ON</t>
+  </si>
+  <si>
+    <t>20135134</t>
+  </si>
+  <si>
+    <t>FRS.CR IN+R/ON MTCHA</t>
+  </si>
+  <si>
+    <t>20062306</t>
+  </si>
+  <si>
+    <t>RXONA MEN DEO ICE 45</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20062309</t>
+  </si>
+  <si>
+    <t>RXNA MEN DEO ULTR 45</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20062307</t>
+  </si>
+  <si>
+    <t>RXONA MEN DEO INV 50</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>20062308</t>
+  </si>
+  <si>
+    <t>RXONA MEN DEO SPR 45</t>
+  </si>
+  <si>
+    <t>20139354</t>
+  </si>
+  <si>
+    <t>RXONA MEN FR.STRK 40</t>
   </si>
   <si>
     <t>PT,(E-1B)</t>
   </si>
   <si>
-    <t>20129840</t>
-  </si>
-  <si>
-    <t>IDM MIE GRG INDO 88G</t>
-  </si>
-  <si>
-    <t>20129841</t>
-  </si>
-  <si>
-    <t>IDM MIE GRG PDS 92G</t>
-  </si>
-  <si>
-    <t>20091175</t>
-  </si>
-  <si>
-    <t>PEPSODNT KIDS STR 45</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>10037208</t>
-  </si>
-  <si>
-    <t>CLOSE UP MT.FRSH 110</t>
-  </si>
-  <si>
-    <t>20027167</t>
-  </si>
-  <si>
-    <t>IDM FAC.TISSUE NP400</t>
-  </si>
-  <si>
-    <t>20104950</t>
-  </si>
-  <si>
-    <t>RINSO MLTO JP/PCH510</t>
+    <t>20139522</t>
+  </si>
+  <si>
+    <t>RXONA MEN DRY DEF 40</t>
+  </si>
+  <si>
+    <t>20128919</t>
+  </si>
+  <si>
+    <t>MOLTO SFTNR PURE 550</t>
   </si>
   <si>
     <t>PT</t>
   </si>
   <si>
-    <t>20054750</t>
-  </si>
-  <si>
-    <t>RNSO+ML LIQ PRFM 510</t>
-  </si>
-  <si>
-    <t>20093188</t>
-  </si>
-  <si>
-    <t>RINSO MLTO GLD LQ510</t>
-  </si>
-  <si>
-    <t>20122879</t>
-  </si>
-  <si>
-    <t>RNSO MLTO KRN STR510</t>
-  </si>
-  <si>
-    <t>20137793</t>
-  </si>
-  <si>
-    <t>RINSO ROSE FRESH 510</t>
-  </si>
-  <si>
-    <t>20140001</t>
-  </si>
-  <si>
-    <t>RINSO PURE LIQ 510G</t>
-  </si>
-  <si>
-    <t>20112492</t>
-  </si>
-  <si>
-    <t>SUNLIGHT JRK NPS400G</t>
+    <t>20129160</t>
+  </si>
+  <si>
+    <t>MOLTO LUXURY PRF 650</t>
+  </si>
+  <si>
+    <t>20129370</t>
+  </si>
+  <si>
+    <t>MOLTO MORNING FRS550</t>
+  </si>
+  <si>
+    <t>20115145</t>
+  </si>
+  <si>
+    <t>L/BUOY BW JPN.SHS380</t>
+  </si>
+  <si>
+    <t>20120878</t>
+  </si>
+  <si>
+    <t>L/BUOY BW MCH&amp;ALO380</t>
+  </si>
+  <si>
+    <t>20123524</t>
+  </si>
+  <si>
+    <t>LIFE/B 3IN1 ABAC 450</t>
+  </si>
+  <si>
+    <t>20141446</t>
+  </si>
+  <si>
+    <t>LFBUOY BW FIFA 360G</t>
   </si>
 </sst>
 </file>
@@ -553,7 +637,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -620,15 +704,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -637,10 +721,10 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -660,7 +744,7 @@
         <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -677,18 +761,18 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>20</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -697,38 +781,38 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -737,18 +821,18 @@
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -760,127 +844,127 @@
         <v>8</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F14" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F15" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="C16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F16" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -894,13 +978,13 @@
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -914,13 +998,13 @@
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -934,33 +1018,253 @@
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" s="1" t="s">
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>37</v>
+      <c r="E25" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/E/TH1MKT.xlsx
+++ b/E/TH1MKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="36">
   <si>
     <t/>
   </si>
   <si>
-    <t>20138893</t>
-  </si>
-  <si>
-    <t>AMO DRMY STRAW 180ML</t>
+    <t>10003091</t>
+  </si>
+  <si>
+    <t>SOSRO CELUP BLCT30X2</t>
   </si>
   <si>
     <t>TH1MKT</t>
@@ -28,223 +28,97 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>10005009</t>
+  </si>
+  <si>
+    <t>POCI TEH CELUP 25X2G</t>
+  </si>
+  <si>
+    <t>10022742</t>
+  </si>
+  <si>
+    <t>POCI TEH CLP VNL25X2</t>
+  </si>
+  <si>
+    <t>20002504</t>
+  </si>
+  <si>
+    <t>ADEM SARI BOX 5'S</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20138894</t>
-  </si>
-  <si>
-    <t>AMO FIZZY EASY 180ML</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>20003567</t>
-  </si>
-  <si>
-    <t>SASA T.BUMBU ORG 210</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20003568</t>
-  </si>
-  <si>
-    <t>SASA T.BUMBU SPIC210</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20014694</t>
-  </si>
-  <si>
-    <t>SASA TPNG G.PISNG210</t>
-  </si>
-  <si>
-    <t>20041881</t>
-  </si>
-  <si>
-    <t>SASA T.BMB KENTKY200</t>
-  </si>
-  <si>
-    <t>20065236</t>
-  </si>
-  <si>
-    <t>SASA TPNG BKWAN 225G</t>
-  </si>
-  <si>
-    <t>10000726</t>
-  </si>
-  <si>
-    <t>ASTOR CHOCOLATE 150G</t>
-  </si>
-  <si>
-    <t>20137700</t>
-  </si>
-  <si>
-    <t>MAYASI CSHW KTCY 35G</t>
-  </si>
-  <si>
-    <t>10037405</t>
-  </si>
-  <si>
-    <t>C/LANG KAYU PUTIH 30</t>
-  </si>
-  <si>
-    <t>RT,(E-6B)</t>
-  </si>
-  <si>
-    <t>20139593</t>
-  </si>
-  <si>
-    <t>FCARE VPOBALM MATCHA</t>
+    <t>20029222</t>
+  </si>
+  <si>
+    <t>PRONAS CORNED BEEF50</t>
   </si>
   <si>
     <t>RT,(E-4B)</t>
   </si>
   <si>
-    <t>20037203</t>
-  </si>
-  <si>
-    <t>FRESH/C MYK ANG LV10</t>
-  </si>
-  <si>
-    <t>20040719</t>
-  </si>
-  <si>
-    <t>FRESH/C MYK/A STRG10</t>
-  </si>
-  <si>
-    <t>20139612</t>
-  </si>
-  <si>
-    <t>FCARE SMASH FRUITY</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20034536</t>
-  </si>
-  <si>
-    <t>FRESH/C MNYK ANGIN10</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20131218</t>
-  </si>
-  <si>
-    <t>FRS.CR SMASH IN+R/ON</t>
-  </si>
-  <si>
-    <t>20135134</t>
-  </si>
-  <si>
-    <t>FRS.CR IN+R/ON MTCHA</t>
-  </si>
-  <si>
-    <t>20062306</t>
-  </si>
-  <si>
-    <t>RXONA MEN DEO ICE 45</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20062309</t>
-  </si>
-  <si>
-    <t>RXNA MEN DEO ULTR 45</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20062307</t>
-  </si>
-  <si>
-    <t>RXONA MEN DEO INV 50</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>20062308</t>
-  </si>
-  <si>
-    <t>RXONA MEN DEO SPR 45</t>
-  </si>
-  <si>
-    <t>20139354</t>
-  </si>
-  <si>
-    <t>RXONA MEN FR.STRK 40</t>
+    <t>20031775</t>
+  </si>
+  <si>
+    <t>NISSIN GEKIKARA 109G</t>
+  </si>
+  <si>
+    <t>20040313</t>
+  </si>
+  <si>
+    <t>MY BABY TELON PLUS30</t>
+  </si>
+  <si>
+    <t>20067395</t>
+  </si>
+  <si>
+    <t>NISSIN GEKI.GRNG 118</t>
+  </si>
+  <si>
+    <t>20091326</t>
+  </si>
+  <si>
+    <t>PLOSSA P&amp;S ECALYPT10</t>
+  </si>
+  <si>
+    <t>20104155</t>
+  </si>
+  <si>
+    <t>NISSIN HOT CARBO 120</t>
+  </si>
+  <si>
+    <t>20112492</t>
+  </si>
+  <si>
+    <t>SUNLIGHT JRK NPS400G</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20122013</t>
+  </si>
+  <si>
+    <t>PLOSSA P&amp;S CITRUS 10</t>
+  </si>
+  <si>
+    <t>20139596</t>
+  </si>
+  <si>
+    <t>PPSODNT SENSI EXP 60</t>
   </si>
   <si>
     <t>PT,(E-1B)</t>
   </si>
   <si>
-    <t>20139522</t>
-  </si>
-  <si>
-    <t>RXONA MEN DRY DEF 40</t>
-  </si>
-  <si>
-    <t>20128919</t>
-  </si>
-  <si>
-    <t>MOLTO SFTNR PURE 550</t>
-  </si>
-  <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>20129160</t>
-  </si>
-  <si>
-    <t>MOLTO LUXURY PRF 650</t>
-  </si>
-  <si>
-    <t>20129370</t>
-  </si>
-  <si>
-    <t>MOLTO MORNING FRS550</t>
-  </si>
-  <si>
-    <t>20115145</t>
-  </si>
-  <si>
-    <t>L/BUOY BW JPN.SHS380</t>
-  </si>
-  <si>
-    <t>20120878</t>
-  </si>
-  <si>
-    <t>L/BUOY BW MCH&amp;ALO380</t>
-  </si>
-  <si>
-    <t>20123524</t>
-  </si>
-  <si>
-    <t>LIFE/B 3IN1 ABAC 450</t>
-  </si>
-  <si>
-    <t>20141446</t>
-  </si>
-  <si>
-    <t>LFBUOY BW FIFA 360G</t>
+    <t>20141330</t>
+  </si>
+  <si>
+    <t>PLOSSA DUAL SRGHAEYO</t>
   </si>
 </sst>
 </file>
@@ -637,7 +511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -701,7 +575,7 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>5</v>
@@ -709,11 +583,11 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
@@ -721,18 +595,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -741,7 +615,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>12</v>
@@ -749,10 +623,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -761,18 +635,18 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -781,7 +655,7 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>12</v>
@@ -789,10 +663,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -801,47 +675,47 @@
         <v>4</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>5</v>
@@ -849,422 +723,102 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>60</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/E/TH1MKT.xlsx
+++ b/E/TH1MKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="40">
   <si>
     <t/>
   </si>
   <si>
-    <t>10003091</t>
-  </si>
-  <si>
-    <t>SOSRO CELUP BLCT30X2</t>
+    <t>10036562</t>
+  </si>
+  <si>
+    <t>GAGA CHILI&amp;TOMAT 155</t>
   </si>
   <si>
     <t>TH1MKT</t>
@@ -28,67 +28,100 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>10005073</t>
+  </si>
+  <si>
+    <t>BLUE BAND PCK 200G</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20025762</t>
+  </si>
+  <si>
+    <t>PIATTOS SAPI PNG 65G</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20094328</t>
+  </si>
+  <si>
+    <t>PIATTOS SMB GPREK 65</t>
+  </si>
+  <si>
+    <t>20138468</t>
+  </si>
+  <si>
+    <t>ROMA MALKS KPYOR 105</t>
+  </si>
+  <si>
+    <t>10002989</t>
+  </si>
+  <si>
+    <t>INDOFOOD SBL PDS 135</t>
+  </si>
+  <si>
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>10005009</t>
-  </si>
-  <si>
-    <t>POCI TEH CELUP 25X2G</t>
-  </si>
-  <si>
-    <t>10022742</t>
-  </si>
-  <si>
-    <t>POCI TEH CLP VNL25X2</t>
-  </si>
-  <si>
-    <t>20002504</t>
-  </si>
-  <si>
-    <t>ADEM SARI BOX 5'S</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20029222</t>
-  </si>
-  <si>
-    <t>PRONAS CORNED BEEF50</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20031775</t>
-  </si>
-  <si>
-    <t>NISSIN GEKIKARA 109G</t>
-  </si>
-  <si>
-    <t>20040313</t>
-  </si>
-  <si>
-    <t>MY BABY TELON PLUS30</t>
-  </si>
-  <si>
-    <t>20067395</t>
-  </si>
-  <si>
-    <t>NISSIN GEKI.GRNG 118</t>
-  </si>
-  <si>
-    <t>20091326</t>
-  </si>
-  <si>
-    <t>PLOSSA P&amp;S ECALYPT10</t>
-  </si>
-  <si>
-    <t>20104155</t>
-  </si>
-  <si>
-    <t>NISSIN HOT CARBO 120</t>
+    <t>20010272</t>
+  </si>
+  <si>
+    <t>INDOFOOD SMB EXT 135</t>
+  </si>
+  <si>
+    <t>20139784</t>
+  </si>
+  <si>
+    <t>ROYCO SOTO AYAM 40G</t>
+  </si>
+  <si>
+    <t>20139801</t>
+  </si>
+  <si>
+    <t>ROYCO RENDANG 45G</t>
+  </si>
+  <si>
+    <t>20139802</t>
+  </si>
+  <si>
+    <t>ROYCO OPOR AYAM 45G</t>
+  </si>
+  <si>
+    <t>20139550</t>
+  </si>
+  <si>
+    <t>REGEN LMN LIME 300ML</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20141124</t>
+  </si>
+  <si>
+    <t>REGEN ORANGE 300ML</t>
+  </si>
+  <si>
+    <t>10037405</t>
+  </si>
+  <si>
+    <t>C/LANG KAYU PUTIH 30</t>
+  </si>
+  <si>
+    <t>RT,(E-6B)</t>
   </si>
   <si>
     <t>20112492</t>
@@ -98,27 +131,6 @@
   </si>
   <si>
     <t>PT</t>
-  </si>
-  <si>
-    <t>20122013</t>
-  </si>
-  <si>
-    <t>PLOSSA P&amp;S CITRUS 10</t>
-  </si>
-  <si>
-    <t>20139596</t>
-  </si>
-  <si>
-    <t>PPSODNT SENSI EXP 60</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20141330</t>
-  </si>
-  <si>
-    <t>PLOSSA DUAL SRGHAEYO</t>
   </si>
 </sst>
 </file>
@@ -575,18 +587,18 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -595,18 +607,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -615,210 +627,210 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/E/TH1MKT.xlsx
+++ b/E/TH1MKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="36">
   <si>
     <t/>
   </si>
   <si>
-    <t>10036562</t>
-  </si>
-  <si>
-    <t>GAGA CHILI&amp;TOMAT 155</t>
+    <t>10002350</t>
+  </si>
+  <si>
+    <t>ABC KCP MANIS TGG275</t>
   </si>
   <si>
     <t>TH1MKT</t>
@@ -28,109 +28,97 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20079510</t>
+  </si>
+  <si>
+    <t>YUPI BREAKFAST 95G</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>10008620</t>
+  </si>
+  <si>
+    <t>YUPI MINI BURGER 105</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>10013885</t>
+  </si>
+  <si>
+    <t>YUPI GUMMY LUNCH 93</t>
+  </si>
+  <si>
+    <t>10004336</t>
+  </si>
+  <si>
+    <t>INDOMARET AIR MIN600</t>
+  </si>
+  <si>
+    <t>PT,(E-1H)</t>
+  </si>
+  <si>
+    <t>20134968</t>
+  </si>
+  <si>
+    <t>COLLAGENA STERIL189</t>
+  </si>
+  <si>
+    <t>20027167</t>
+  </si>
+  <si>
+    <t>IDM FAC.TISSUE NP400</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20108708</t>
+  </si>
+  <si>
+    <t>PEPSODENT COMP8 150G</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20062306</t>
+  </si>
+  <si>
+    <t>RXONA MEN DEO ICE 45</t>
+  </si>
+  <si>
+    <t>20137510</t>
+  </si>
+  <si>
+    <t>C/LANG KY PTH ROL 15</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>RT,(E-4B)</t>
   </si>
   <si>
-    <t>10005073</t>
-  </si>
-  <si>
-    <t>BLUE BAND PCK 200G</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20025762</t>
-  </si>
-  <si>
-    <t>PIATTOS SAPI PNG 65G</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20094328</t>
-  </si>
-  <si>
-    <t>PIATTOS SMB GPREK 65</t>
-  </si>
-  <si>
-    <t>20138468</t>
-  </si>
-  <si>
-    <t>ROMA MALKS KPYOR 105</t>
-  </si>
-  <si>
-    <t>10002989</t>
-  </si>
-  <si>
-    <t>INDOFOOD SBL PDS 135</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20010272</t>
-  </si>
-  <si>
-    <t>INDOFOOD SMB EXT 135</t>
-  </si>
-  <si>
-    <t>20139784</t>
-  </si>
-  <si>
-    <t>ROYCO SOTO AYAM 40G</t>
-  </si>
-  <si>
-    <t>20139801</t>
-  </si>
-  <si>
-    <t>ROYCO RENDANG 45G</t>
-  </si>
-  <si>
-    <t>20139802</t>
-  </si>
-  <si>
-    <t>ROYCO OPOR AYAM 45G</t>
-  </si>
-  <si>
-    <t>20139550</t>
-  </si>
-  <si>
-    <t>REGEN LMN LIME 300ML</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20141124</t>
-  </si>
-  <si>
-    <t>REGEN ORANGE 300ML</t>
-  </si>
-  <si>
-    <t>10037405</t>
-  </si>
-  <si>
-    <t>C/LANG KAYU PUTIH 30</t>
-  </si>
-  <si>
-    <t>RT,(E-6B)</t>
-  </si>
-  <si>
-    <t>20112492</t>
-  </si>
-  <si>
-    <t>SUNLIGHT JRK NPS400G</t>
-  </si>
-  <si>
-    <t>PT</t>
+    <t>20131788</t>
+  </si>
+  <si>
+    <t>MAMA LMN JR.NPS 950</t>
+  </si>
+  <si>
+    <t>20142275</t>
+  </si>
+  <si>
+    <t>MAMA LIME CHARCO 950</t>
   </si>
 </sst>
 </file>
@@ -523,7 +511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -610,15 +598,15 @@
         <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -630,15 +618,15 @@
         <v>12</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -650,7 +638,7 @@
         <v>4</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -670,27 +658,27 @@
         <v>8</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -704,70 +692,70 @@
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="F9" s="1" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="E12" s="1" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>9</v>
@@ -775,62 +763,22 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/E/TH1MKT.xlsx
+++ b/E/TH1MKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="59">
   <si>
     <t/>
   </si>
   <si>
-    <t>10002350</t>
-  </si>
-  <si>
-    <t>ABC KCP MANIS TGG275</t>
+    <t>10032310</t>
+  </si>
+  <si>
+    <t>CHUPA CHUPS LOLLIPOP</t>
   </si>
   <si>
     <t>TH1MKT</t>
@@ -28,97 +28,166 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20079510</t>
-  </si>
-  <si>
-    <t>YUPI BREAKFAST 95G</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20139431</t>
+  </si>
+  <si>
+    <t>PRMINA YGR MLT MLK 8</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>10008620</t>
-  </si>
-  <si>
-    <t>YUPI MINI BURGER 105</t>
+    <t>20139421</t>
+  </si>
+  <si>
+    <t>PRMINA YGR MLT SRW 8</t>
+  </si>
+  <si>
+    <t>20141837</t>
+  </si>
+  <si>
+    <t>PEPSODENT PG FIFA95</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>10013885</t>
-  </si>
-  <si>
-    <t>YUPI GUMMY LUNCH 93</t>
-  </si>
-  <si>
-    <t>10004336</t>
-  </si>
-  <si>
-    <t>INDOMARET AIR MIN600</t>
-  </si>
-  <si>
-    <t>PT,(E-1H)</t>
-  </si>
-  <si>
-    <t>20134968</t>
-  </si>
-  <si>
-    <t>COLLAGENA STERIL189</t>
-  </si>
-  <si>
-    <t>20027167</t>
-  </si>
-  <si>
-    <t>IDM FAC.TISSUE NP400</t>
-  </si>
-  <si>
     <t>PT,(E-1B)</t>
   </si>
   <si>
-    <t>20108708</t>
-  </si>
-  <si>
-    <t>PEPSODENT COMP8 150G</t>
+    <t>20120206</t>
+  </si>
+  <si>
+    <t>PPSODENT PG HRBL 150</t>
   </si>
   <si>
     <t>PT,(E-3B)</t>
   </si>
   <si>
+    <t>20054969</t>
+  </si>
+  <si>
+    <t>ANTANGIN GNGR/M 5X15</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20114432</t>
+  </si>
+  <si>
+    <t>ANTANGIN HTBTSDA 5'S</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20062309</t>
+  </si>
+  <si>
+    <t>RXNA MEN DEO ULTR 45</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
     <t>20062306</t>
   </si>
   <si>
     <t>RXONA MEN DEO ICE 45</t>
   </si>
   <si>
-    <t>20137510</t>
-  </si>
-  <si>
-    <t>C/LANG KY PTH ROL 15</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20131788</t>
-  </si>
-  <si>
-    <t>MAMA LMN JR.NPS 950</t>
-  </si>
-  <si>
-    <t>20142275</t>
-  </si>
-  <si>
-    <t>MAMA LIME CHARCO 950</t>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20062307</t>
+  </si>
+  <si>
+    <t>RXONA MEN DEO INV 50</t>
+  </si>
+  <si>
+    <t>20062308</t>
+  </si>
+  <si>
+    <t>RXONA MEN DEO SPR 45</t>
+  </si>
+  <si>
+    <t>20076987</t>
+  </si>
+  <si>
+    <t>BAYGON FLOW.GRDN 200</t>
+  </si>
+  <si>
+    <t>RT,(E-3.5B)</t>
+  </si>
+  <si>
+    <t>10040202</t>
+  </si>
+  <si>
+    <t>SOFFELL A.NYMK K/J60</t>
+  </si>
+  <si>
+    <t>20078241</t>
+  </si>
+  <si>
+    <t>SOFFELL LOT.APEL 60G</t>
+  </si>
+  <si>
+    <t>20128713</t>
+  </si>
+  <si>
+    <t>SOFEL LOT.KRN/SMR 60</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20141329</t>
+  </si>
+  <si>
+    <t>SO FRSH CTRUS 2X10ML</t>
+  </si>
+  <si>
+    <t>20134253</t>
+  </si>
+  <si>
+    <t>SO FRSH HOT 2X10ML</t>
+  </si>
+  <si>
+    <t>20134254</t>
+  </si>
+  <si>
+    <t>SO FRSH EUCLYP2X10ML</t>
+  </si>
+  <si>
+    <t>20141441</t>
+  </si>
+  <si>
+    <t>C.LANG MK.BAYI LVD60</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>10037405</t>
+  </si>
+  <si>
+    <t>C/LANG KAYU PUTIH 30</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>RT,(E-6B)</t>
+  </si>
+  <si>
+    <t>20141440</t>
+  </si>
+  <si>
+    <t>C.LANG MK BAYI CHM60</t>
   </si>
 </sst>
 </file>
@@ -511,14 +580,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -572,53 +641,53 @@
         <v>3</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="E5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -632,10 +701,10 @@
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>17</v>
@@ -652,93 +721,93 @@
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="F11" s="1" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -752,13 +821,13 @@
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -772,13 +841,193 @@
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>9</v>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/E/TH1MKT.xlsx
+++ b/E/TH1MKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="53">
   <si>
     <t/>
   </si>
   <si>
-    <t>10032310</t>
-  </si>
-  <si>
-    <t>CHUPA CHUPS LOLLIPOP</t>
+    <t>20120928</t>
+  </si>
+  <si>
+    <t>IM-BOOST VIT C&amp;D3 4S</t>
   </si>
   <si>
     <t>TH1MKT</t>
@@ -28,166 +28,148 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>10004394</t>
+  </si>
+  <si>
+    <t>MENTOS FRUIT ROLL 37</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20139431</t>
-  </si>
-  <si>
-    <t>PRMINA YGR MLT MLK 8</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>20139421</t>
-  </si>
-  <si>
-    <t>PRMINA YGR MLT SRW 8</t>
-  </si>
-  <si>
-    <t>20141837</t>
-  </si>
-  <si>
-    <t>PEPSODENT PG FIFA95</t>
+    <t>10030201</t>
+  </si>
+  <si>
+    <t>MENTOS CND ROL AGR37</t>
+  </si>
+  <si>
+    <t>10036998</t>
+  </si>
+  <si>
+    <t>MENTOS MINT ROLL 37G</t>
+  </si>
+  <si>
+    <t>20139074</t>
+  </si>
+  <si>
+    <t>MENTOS BERRY GD 37.8</t>
+  </si>
+  <si>
+    <t>20031983</t>
+  </si>
+  <si>
+    <t>MENTOS RAINBOW 37G</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20120206</t>
-  </si>
-  <si>
-    <t>PPSODENT PG HRBL 150</t>
+    <t>10016646</t>
+  </si>
+  <si>
+    <t>INDO/F KECAP MN.R725</t>
+  </si>
+  <si>
+    <t>20002987</t>
+  </si>
+  <si>
+    <t>KUSUKA KRP BARBQU 60</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20002988</t>
+  </si>
+  <si>
+    <t>KUSUKA KRP AYM LD 60</t>
+  </si>
+  <si>
+    <t>20026343</t>
+  </si>
+  <si>
+    <t>KUSUKA RMPT LAUT 60</t>
+  </si>
+  <si>
+    <t>20044334</t>
+  </si>
+  <si>
+    <t>SOSRO TEH BTL TPK300</t>
+  </si>
+  <si>
+    <t>20138071</t>
+  </si>
+  <si>
+    <t>KISPRAY KASTURI 280</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20074721</t>
+  </si>
+  <si>
+    <t>KISPRAY GLM.GOLD 280</t>
+  </si>
+  <si>
+    <t>20032250</t>
+  </si>
+  <si>
+    <t>KISPRAY VIOLET PC280</t>
+  </si>
+  <si>
+    <t>20112492</t>
+  </si>
+  <si>
+    <t>SUNLIGHT JRK NPS400G</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20062311</t>
+  </si>
+  <si>
+    <t>REXONA DEO F.SPRT 45</t>
   </si>
   <si>
     <t>PT,(E-3B)</t>
   </si>
   <si>
-    <t>20054969</t>
-  </si>
-  <si>
-    <t>ANTANGIN GNGR/M 5X15</t>
+    <t>20062312</t>
+  </si>
+  <si>
+    <t>REXONA DEO INV.DR 45</t>
+  </si>
+  <si>
+    <t>20062314</t>
+  </si>
+  <si>
+    <t>REXONA DEO SHW.CL 45</t>
+  </si>
+  <si>
+    <t>20062411</t>
+  </si>
+  <si>
+    <t>REXONA DEO PWDR DR45</t>
+  </si>
+  <si>
+    <t>20137510</t>
+  </si>
+  <si>
+    <t>C/LANG KY PTH ROL 15</t>
   </si>
   <si>
     <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20114432</t>
-  </si>
-  <si>
-    <t>ANTANGIN HTBTSDA 5'S</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20062309</t>
-  </si>
-  <si>
-    <t>RXNA MEN DEO ULTR 45</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20062306</t>
-  </si>
-  <si>
-    <t>RXONA MEN DEO ICE 45</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20062307</t>
-  </si>
-  <si>
-    <t>RXONA MEN DEO INV 50</t>
-  </si>
-  <si>
-    <t>20062308</t>
-  </si>
-  <si>
-    <t>RXONA MEN DEO SPR 45</t>
-  </si>
-  <si>
-    <t>20076987</t>
-  </si>
-  <si>
-    <t>BAYGON FLOW.GRDN 200</t>
-  </si>
-  <si>
-    <t>RT,(E-3.5B)</t>
-  </si>
-  <si>
-    <t>10040202</t>
-  </si>
-  <si>
-    <t>SOFFELL A.NYMK K/J60</t>
-  </si>
-  <si>
-    <t>20078241</t>
-  </si>
-  <si>
-    <t>SOFFELL LOT.APEL 60G</t>
-  </si>
-  <si>
-    <t>20128713</t>
-  </si>
-  <si>
-    <t>SOFEL LOT.KRN/SMR 60</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20141329</t>
-  </si>
-  <si>
-    <t>SO FRSH CTRUS 2X10ML</t>
-  </si>
-  <si>
-    <t>20134253</t>
-  </si>
-  <si>
-    <t>SO FRSH HOT 2X10ML</t>
-  </si>
-  <si>
-    <t>20134254</t>
-  </si>
-  <si>
-    <t>SO FRSH EUCLYP2X10ML</t>
-  </si>
-  <si>
-    <t>20141441</t>
-  </si>
-  <si>
-    <t>C.LANG MK.BAYI LVD60</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>10037405</t>
-  </si>
-  <si>
-    <t>C/LANG KAYU PUTIH 30</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>RT,(E-6B)</t>
-  </si>
-  <si>
-    <t>20141440</t>
-  </si>
-  <si>
-    <t>C.LANG MK BAYI CHM60</t>
   </si>
 </sst>
 </file>
@@ -580,14 +562,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -641,350 +623,350 @@
         <v>3</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="F7" s="1" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>5</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>5</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>5</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>43</v>
@@ -992,42 +974,22 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/E/TH1MKT.xlsx
+++ b/E/TH1MKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="42">
   <si>
     <t/>
   </si>
   <si>
-    <t>20120928</t>
-  </si>
-  <si>
-    <t>IM-BOOST VIT C&amp;D3 4S</t>
+    <t>20025762</t>
+  </si>
+  <si>
+    <t>PIATTOS SAPI PNG 65G</t>
   </si>
   <si>
     <t>TH1MKT</t>
@@ -28,148 +28,115 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20094328</t>
+  </si>
+  <si>
+    <t>PIATTOS SMB GPREK 65</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>20132660</t>
+  </si>
+  <si>
+    <t>2 BELIBIS SAUS 235ML</t>
+  </si>
+  <si>
+    <t>20141500</t>
+  </si>
+  <si>
+    <t>2 BELIBIS EX/PDS 235</t>
+  </si>
+  <si>
+    <t>20141501</t>
+  </si>
+  <si>
+    <t>2 BELIBIS PDS LD 235</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>20121168</t>
+  </si>
+  <si>
+    <t>RICOLA LEMON MINT 40</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20121182</t>
+  </si>
+  <si>
+    <t>RICOLA GLACIER FM 40</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20113135</t>
+  </si>
+  <si>
+    <t>AMUNIZER BTL 140ML</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>10004394</t>
-  </si>
-  <si>
-    <t>MENTOS FRUIT ROLL 37</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>10030201</t>
-  </si>
-  <si>
-    <t>MENTOS CND ROL AGR37</t>
-  </si>
-  <si>
-    <t>10036998</t>
-  </si>
-  <si>
-    <t>MENTOS MINT ROLL 37G</t>
-  </si>
-  <si>
-    <t>20139074</t>
-  </si>
-  <si>
-    <t>MENTOS BERRY GD 37.8</t>
-  </si>
-  <si>
-    <t>20031983</t>
-  </si>
-  <si>
-    <t>MENTOS RAINBOW 37G</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>10016646</t>
-  </si>
-  <si>
-    <t>INDO/F KECAP MN.R725</t>
-  </si>
-  <si>
-    <t>20002987</t>
-  </si>
-  <si>
-    <t>KUSUKA KRP BARBQU 60</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20002988</t>
-  </si>
-  <si>
-    <t>KUSUKA KRP AYM LD 60</t>
-  </si>
-  <si>
-    <t>20026343</t>
-  </si>
-  <si>
-    <t>KUSUKA RMPT LAUT 60</t>
-  </si>
-  <si>
-    <t>20044334</t>
-  </si>
-  <si>
-    <t>SOSRO TEH BTL TPK300</t>
-  </si>
-  <si>
-    <t>20138071</t>
-  </si>
-  <si>
-    <t>KISPRAY KASTURI 280</t>
-  </si>
-  <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>20074721</t>
-  </si>
-  <si>
-    <t>KISPRAY GLM.GOLD 280</t>
-  </si>
-  <si>
-    <t>20032250</t>
-  </si>
-  <si>
-    <t>KISPRAY VIOLET PC280</t>
+    <t>20078101</t>
+  </si>
+  <si>
+    <t>EMERON HAIR/V PINK6S</t>
+  </si>
+  <si>
+    <t>20139596</t>
+  </si>
+  <si>
+    <t>PPSODNT SENSI EXP 60</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20142282</t>
+  </si>
+  <si>
+    <t>CLOSEUP PG FIFA 95G</t>
+  </si>
+  <si>
+    <t>20019446</t>
+  </si>
+  <si>
+    <t>C/LANG MINYAK GPU 60</t>
+  </si>
+  <si>
+    <t>RT,(E-6B)</t>
+  </si>
+  <si>
+    <t>20140802</t>
+  </si>
+  <si>
+    <t>IDM TISU DAPUR 1+1</t>
+  </si>
+  <si>
+    <t>PT</t>
   </si>
   <si>
     <t>20112492</t>
   </si>
   <si>
     <t>SUNLIGHT JRK NPS400G</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>20062311</t>
-  </si>
-  <si>
-    <t>REXONA DEO F.SPRT 45</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20062312</t>
-  </si>
-  <si>
-    <t>REXONA DEO INV.DR 45</t>
-  </si>
-  <si>
-    <t>20062314</t>
-  </si>
-  <si>
-    <t>REXONA DEO SHW.CL 45</t>
-  </si>
-  <si>
-    <t>20062411</t>
-  </si>
-  <si>
-    <t>REXONA DEO PWDR DR45</t>
-  </si>
-  <si>
-    <t>20137510</t>
-  </si>
-  <si>
-    <t>C/LANG KY PTH ROL 15</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
   </si>
 </sst>
 </file>
@@ -562,7 +529,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -629,67 +596,67 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F4" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F6" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -703,41 +670,41 @@
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -746,98 +713,98 @@
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F13" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -846,18 +813,18 @@
         <v>18</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -866,130 +833,10 @@
         <v>18</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/E/TH1MKT.xlsx
+++ b/E/TH1MKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="44">
   <si>
     <t/>
   </si>
   <si>
-    <t>20025762</t>
-  </si>
-  <si>
-    <t>PIATTOS SAPI PNG 65G</t>
+    <t>20112944</t>
+  </si>
+  <si>
+    <t>IDM KUACI SUSU 80G</t>
   </si>
   <si>
     <t>TH1MKT</t>
@@ -28,115 +28,121 @@
     <t>1</t>
   </si>
   <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20093516</t>
+  </si>
+  <si>
+    <t>INDOMARET KUACI 80G</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>20044334</t>
+  </si>
+  <si>
+    <t>SOSRO TEH BTL TPK300</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>10002350</t>
+  </si>
+  <si>
+    <t>ABC KCP MANIS TGG275</t>
+  </si>
+  <si>
     <t>RT,(E-2B)</t>
   </si>
   <si>
-    <t>20094328</t>
-  </si>
-  <si>
-    <t>PIATTOS SMB GPREK 65</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>20132660</t>
-  </si>
-  <si>
-    <t>2 BELIBIS SAUS 235ML</t>
-  </si>
-  <si>
-    <t>20141500</t>
-  </si>
-  <si>
-    <t>2 BELIBIS EX/PDS 235</t>
-  </si>
-  <si>
-    <t>20141501</t>
-  </si>
-  <si>
-    <t>2 BELIBIS PDS LD 235</t>
+    <t>20142410</t>
+  </si>
+  <si>
+    <t>EMRN B/RM APR ORG400</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>20121168</t>
-  </si>
-  <si>
-    <t>RICOLA LEMON MINT 40</t>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>10037208</t>
+  </si>
+  <si>
+    <t>CLOSE UP MT.FRSH 100</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20136643</t>
+  </si>
+  <si>
+    <t>PSODENT PG STRG 190G</t>
+  </si>
+  <si>
+    <t>10037405</t>
+  </si>
+  <si>
+    <t>C/LANG KAYU PUTIH 30</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20121182</t>
-  </si>
-  <si>
-    <t>RICOLA GLACIER FM 40</t>
+    <t>RT,(E-6B)</t>
+  </si>
+  <si>
+    <t>20141440</t>
+  </si>
+  <si>
+    <t>C.LANG MK BAYI CHM60</t>
+  </si>
+  <si>
+    <t>20141441</t>
+  </si>
+  <si>
+    <t>C.LANG MK.BAYI LVD60</t>
+  </si>
+  <si>
+    <t>20141330</t>
+  </si>
+  <si>
+    <t>PLOSSA DUAL SRGHAEYO</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>20113135</t>
-  </si>
-  <si>
-    <t>AMUNIZER BTL 140ML</t>
+    <t>20091326</t>
+  </si>
+  <si>
+    <t>PLOSSA P&amp;S ECALYPT10</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20078101</t>
-  </si>
-  <si>
-    <t>EMERON HAIR/V PINK6S</t>
-  </si>
-  <si>
-    <t>20139596</t>
-  </si>
-  <si>
-    <t>PPSODNT SENSI EXP 60</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20142282</t>
-  </si>
-  <si>
-    <t>CLOSEUP PG FIFA 95G</t>
-  </si>
-  <si>
-    <t>20019446</t>
-  </si>
-  <si>
-    <t>C/LANG MINYAK GPU 60</t>
-  </si>
-  <si>
-    <t>RT,(E-6B)</t>
-  </si>
-  <si>
-    <t>20140802</t>
-  </si>
-  <si>
-    <t>IDM TISU DAPUR 1+1</t>
+    <t>20098520</t>
+  </si>
+  <si>
+    <t>IDM TISSUE PNGST 150</t>
   </si>
   <si>
     <t>PT</t>
   </si>
   <si>
-    <t>20112492</t>
-  </si>
-  <si>
-    <t>SUNLIGHT JRK NPS400G</t>
+    <t>20138518</t>
+  </si>
+  <si>
+    <t>KILAU NIPIS 630ML</t>
+  </si>
+  <si>
+    <t>RT,(E-1.5B)</t>
   </si>
 </sst>
 </file>
@@ -529,17 +535,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -558,8 +565,14 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -575,11 +588,11 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -595,11 +608,11 @@
       <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -615,16 +628,16 @@
       <c r="E4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H4" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -635,131 +648,131 @@
       <c r="E5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H5" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="1" t="s">
+      <c r="H7" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="1" t="s">
+      <c r="E8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" s="1" t="s">
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H11" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>32</v>
       </c>
@@ -770,73 +783,73 @@
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H13" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F13" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F14" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H14" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="1" t="s">
-        <v>39</v>
+      <c r="H15" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/E/TH1MKT.xlsx
+++ b/E/TH1MKT.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="44">
   <si>
     <t/>
   </si>
@@ -535,18 +535,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="13" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -565,14 +564,8 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -588,11 +581,11 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -608,11 +601,11 @@
       <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -628,11 +621,11 @@
       <c r="E4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
@@ -648,11 +641,11 @@
       <c r="E5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -668,11 +661,11 @@
       <c r="E6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
@@ -688,11 +681,11 @@
       <c r="E7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>22</v>
       </c>
@@ -708,11 +701,11 @@
       <c r="E8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>24</v>
       </c>
@@ -728,11 +721,11 @@
       <c r="E9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>28</v>
       </c>
@@ -748,11 +741,11 @@
       <c r="E10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>30</v>
       </c>
@@ -768,11 +761,11 @@
       <c r="E11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="F11" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>32</v>
       </c>
@@ -788,11 +781,11 @@
       <c r="E12" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="F12" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>35</v>
       </c>
@@ -808,11 +801,11 @@
       <c r="E13" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="F13" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>38</v>
       </c>
@@ -828,11 +821,11 @@
       <c r="E14" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="F14" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>41</v>
       </c>
@@ -848,7 +841,7 @@
       <c r="E15" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="F15" s="1" t="s">
         <v>43</v>
       </c>
     </row>

--- a/E/TH1MKT.xlsx
+++ b/E/TH1MKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="38">
   <si>
     <t/>
   </si>
   <si>
-    <t>20112944</t>
-  </si>
-  <si>
-    <t>IDM KUACI SUSU 80G</t>
+    <t>20037131</t>
+  </si>
+  <si>
+    <t>PRIM-A AIR MNRAL 600</t>
   </si>
   <si>
     <t>TH1MKT</t>
@@ -28,121 +28,103 @@
     <t>1</t>
   </si>
   <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20093516</t>
-  </si>
-  <si>
-    <t>INDOMARET KUACI 80G</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>10032310</t>
+  </si>
+  <si>
+    <t>CHUPA CHUPS LOLLIPOP</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20044334</t>
-  </si>
-  <si>
-    <t>SOSRO TEH BTL TPK300</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>10002350</t>
-  </si>
-  <si>
-    <t>ABC KCP MANIS TGG275</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20142410</t>
-  </si>
-  <si>
-    <t>EMRN B/RM APR ORG400</t>
+    <t>20139802</t>
+  </si>
+  <si>
+    <t>ROYCO OPOR AYAM 45G</t>
+  </si>
+  <si>
+    <t>20139784</t>
+  </si>
+  <si>
+    <t>ROYCO SOTO AYAM 40G</t>
+  </si>
+  <si>
+    <t>20139801</t>
+  </si>
+  <si>
+    <t>ROYCO RENDANG 45G</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
+    <t>20136643</t>
+  </si>
+  <si>
+    <t>PSODENT PG STRG 190G</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20120206</t>
+  </si>
+  <si>
+    <t>PPSODENT PG HRBL 150</t>
+  </si>
+  <si>
+    <t>20140679</t>
+  </si>
+  <si>
+    <t>IDM FC.TISSUE 3X80'S</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20120928</t>
+  </si>
+  <si>
+    <t>IM-BOOST VIT C&amp;D3 4S</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>10037208</t>
-  </si>
-  <si>
-    <t>CLOSE UP MT.FRSH 100</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20136643</t>
-  </si>
-  <si>
-    <t>PSODENT PG STRG 190G</t>
-  </si>
-  <si>
-    <t>10037405</t>
-  </si>
-  <si>
-    <t>C/LANG KAYU PUTIH 30</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>RT,(E-6B)</t>
-  </si>
-  <si>
-    <t>20141440</t>
-  </si>
-  <si>
-    <t>C.LANG MK BAYI CHM60</t>
-  </si>
-  <si>
-    <t>20141441</t>
-  </si>
-  <si>
-    <t>C.LANG MK.BAYI LVD60</t>
-  </si>
-  <si>
-    <t>20141330</t>
-  </si>
-  <si>
-    <t>PLOSSA DUAL SRGHAEYO</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20091326</t>
-  </si>
-  <si>
-    <t>PLOSSA P&amp;S ECALYPT10</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20098520</t>
-  </si>
-  <si>
-    <t>IDM TISSUE PNGST 150</t>
+    <t>20112492</t>
+  </si>
+  <si>
+    <t>SUNLIGHT JRK NPS400G</t>
   </si>
   <si>
     <t>PT</t>
   </si>
   <si>
-    <t>20138518</t>
-  </si>
-  <si>
-    <t>KILAU NIPIS 630ML</t>
-  </si>
-  <si>
-    <t>RT,(E-1.5B)</t>
+    <t>20114432</t>
+  </si>
+  <si>
+    <t>ANTANGIN HTBTSDA 5'S</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20054969</t>
+  </si>
+  <si>
+    <t>ANTANGIN GNGR/M 5X15</t>
+  </si>
+  <si>
+    <t>20137510</t>
+  </si>
+  <si>
+    <t>C/LANG KY PTH ROL 15</t>
   </si>
 </sst>
 </file>
@@ -535,14 +517,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -622,15 +604,15 @@
         <v>4</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -642,175 +624,175 @@
         <v>8</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F6" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>26</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -819,30 +801,10 @@
         <v>26</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/E/TH1MKT.xlsx
+++ b/E/TH1MKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="42">
   <si>
     <t/>
   </si>
   <si>
-    <t>20053540</t>
-  </si>
-  <si>
-    <t>ADEM SARI CK BTL 350</t>
+    <t>10003091</t>
+  </si>
+  <si>
+    <t>SOSRO CELUP BLCT30X2</t>
   </si>
   <si>
     <t>TH1MKT</t>
@@ -28,199 +28,115 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>10022742</t>
+  </si>
+  <si>
+    <t>POCI TEH CLP VNL25X2</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>10008620</t>
+  </si>
+  <si>
+    <t>YUPI MINI BURGER 105</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20122090</t>
-  </si>
-  <si>
-    <t>ADEM/S MD LMN TEA350</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20112371</t>
-  </si>
-  <si>
-    <t>GADJAH KP.TUBRUK 138</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20112372</t>
-  </si>
-  <si>
-    <t>GADJAH KP.TUBRUK 10S</t>
+    <t>10013885</t>
+  </si>
+  <si>
+    <t>YUPI GUMMY LUNCH 93</t>
+  </si>
+  <si>
+    <t>20079510</t>
+  </si>
+  <si>
+    <t>YUPI BREAKFAST 95G</t>
+  </si>
+  <si>
+    <t>20141464</t>
+  </si>
+  <si>
+    <t>RMN YES HKTA CHKN88G</t>
+  </si>
+  <si>
+    <t>20141466</t>
+  </si>
+  <si>
+    <t>RMN YES TKYO CHKN84G</t>
+  </si>
+  <si>
+    <t>20025762</t>
+  </si>
+  <si>
+    <t>PIATTOS SAPI PNG 65G</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20142077</t>
+  </si>
+  <si>
+    <t>TEH LEMON MADU 350ML</t>
+  </si>
+  <si>
+    <t>20074721</t>
+  </si>
+  <si>
+    <t>KISPRAY GLM.GOLD 280</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20138071</t>
+  </si>
+  <si>
+    <t>KISPRAY KASTURI 280</t>
+  </si>
+  <si>
+    <t>20032250</t>
+  </si>
+  <si>
+    <t>KISPRAY VIOLET PC280</t>
+  </si>
+  <si>
+    <t>20137510</t>
+  </si>
+  <si>
+    <t>C/LANG KY PTH ROL 15</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>20138743</t>
-  </si>
-  <si>
-    <t>ROYAL SS JEJU 55G</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>RT,(E-7H)</t>
-  </si>
-  <si>
-    <t>20138744</t>
-  </si>
-  <si>
-    <t>ROYAL SS DAEGU 55G</t>
-  </si>
-  <si>
-    <t>20138745</t>
-  </si>
-  <si>
-    <t>ROYAL SS NAMI 55G</t>
-  </si>
-  <si>
-    <t>20040276</t>
-  </si>
-  <si>
-    <t>ADEM SARI CK KLG 320</t>
-  </si>
-  <si>
-    <t>20083775</t>
-  </si>
-  <si>
-    <t>ADEMSARI CK HR.T 320</t>
-  </si>
-  <si>
-    <t>20071642</t>
-  </si>
-  <si>
-    <t>ADEMSARI CK SPRK 320</t>
-  </si>
-  <si>
-    <t>20040313</t>
-  </si>
-  <si>
-    <t>MY BABY TELON PLUS30</t>
-  </si>
-  <si>
-    <t>20141440</t>
-  </si>
-  <si>
-    <t>C.LANG MK BAYI CHM60</t>
-  </si>
-  <si>
-    <t>20141441</t>
-  </si>
-  <si>
-    <t>C.LANG MK.BAYI LVD60</t>
-  </si>
-  <si>
-    <t>10037405</t>
-  </si>
-  <si>
-    <t>C/LANG KAYU PUTIH 30</t>
-  </si>
-  <si>
-    <t>RT,(E-6B)</t>
-  </si>
-  <si>
-    <t>20034536</t>
-  </si>
-  <si>
-    <t>FRESH/C MNYK ANGIN10</t>
-  </si>
-  <si>
     <t>RT,(E-4B)</t>
   </si>
   <si>
-    <t>20037203</t>
-  </si>
-  <si>
-    <t>FRESH/C MYK ANG LV10</t>
-  </si>
-  <si>
-    <t>20040719</t>
-  </si>
-  <si>
-    <t>FRESH/C MYK/A STRG10</t>
-  </si>
-  <si>
-    <t>20139593</t>
-  </si>
-  <si>
-    <t>FCARE VPOBALM MATCHA</t>
-  </si>
-  <si>
-    <t>10027167</t>
-  </si>
-  <si>
-    <t>DOVE DEO CMP.CARE 40</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20134770</t>
-  </si>
-  <si>
-    <t>DOVE R/ON SRM+CLG 50</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20142128</t>
-  </si>
-  <si>
-    <t>DOVE SRM RO NIA VITC</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20027167</t>
-  </si>
-  <si>
-    <t>IDM FAC.TISSUE NP400</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20020226</t>
-  </si>
-  <si>
-    <t>MOLTO PWNGI PINK 765</t>
+    <t>20140802</t>
+  </si>
+  <si>
+    <t>IDM TISU DAPUR 1+1</t>
   </si>
   <si>
     <t>PT</t>
   </si>
   <si>
-    <t>20020245</t>
-  </si>
-  <si>
-    <t>MOLTO PWNGI BLUE 765</t>
-  </si>
-  <si>
-    <t>20106821</t>
-  </si>
-  <si>
-    <t>MOLTO PURPLE 765ML</t>
-  </si>
-  <si>
-    <t>20142219</t>
-  </si>
-  <si>
-    <t>MLTO GNTL FRSH 765ML</t>
+    <t>20112492</t>
+  </si>
+  <si>
+    <t>SUNLIGHT JRK NPS400G</t>
   </si>
 </sst>
 </file>
@@ -613,7 +529,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -680,27 +596,27 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -717,19 +633,19 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
@@ -737,58 +653,58 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -797,18 +713,18 @@
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -817,350 +733,130 @@
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="C14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F14" s="1" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>60</v>
       </c>
     </row>
   </sheetData>
